--- a/data/trans_orig/IP36BS1-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP36BS1-Clase-trans_orig.xlsx
@@ -2815,7 +2815,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2781</t>
+          <t>2462</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2830,7 +2830,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>58,1%</t>
+          <t>51,43%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2850,7 +2850,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2913</t>
+          <t>2934</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>40,43%</t>
+          <t>40,72%</t>
         </is>
       </c>
     </row>
@@ -3380,7 +3380,7 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3368</t>
+          <t>3388</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3395,7 +3395,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>70,36%</t>
+          <t>70,77%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3415,7 +3415,7 @@
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>3865</t>
+          <t>3509</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>53,65%</t>
+          <t>48,71%</t>
         </is>
       </c>
     </row>
@@ -3493,7 +3493,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2740</t>
+          <t>2761</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>57,23%</t>
+          <t>57,68%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3528,7 +3528,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3401</t>
+          <t>2859</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3543,7 +3543,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>47,21%</t>
+          <t>39,68%</t>
         </is>
       </c>
     </row>
@@ -3601,12 +3601,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>703</t>
+          <t>704</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>4134</t>
+          <t>4118</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3616,12 +3616,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>86,03%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,12 +3636,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2144</t>
+          <t>2278</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6550</t>
+          <t>6568</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3651,12 +3651,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>31,62%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>91,17%</t>
         </is>
       </c>
     </row>
@@ -4027,7 +4027,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>3085</t>
+          <t>3154</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4042,7 +4042,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>62,83%</t>
+          <t>64,23%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4097,7 +4097,7 @@
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>3571</t>
+          <t>3704</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4112,7 +4112,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>32,78%</t>
         </is>
       </c>
     </row>
@@ -4366,7 +4366,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>3456</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>70,39%</t>
+          <t>74,4%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4401,7 +4401,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>3514</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>50,14%</t>
+          <t>55,0%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>730</t>
+          <t>738</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>5525</t>
+          <t>5459</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4446,12 +4446,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>48,9%</t>
+          <t>48,31%</t>
         </is>
       </c>
     </row>
@@ -4479,7 +4479,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>3060</t>
+          <t>3007</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>62,33%</t>
+          <t>61,24%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4514,7 +4514,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>2633</t>
+          <t>3237</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4529,7 +4529,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>41,21%</t>
+          <t>50,66%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4549,7 +4549,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>4589</t>
+          <t>4193</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4564,7 +4564,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>40,61%</t>
+          <t>37,11%</t>
         </is>
       </c>
     </row>
@@ -4587,12 +4587,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>653</t>
+          <t>625</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>4188</t>
+          <t>4183</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4602,12 +4602,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>85,31%</t>
+          <t>85,18%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4622,12 +4622,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>2519</t>
+          <t>2486</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>5914</t>
+          <t>5906</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4637,12 +4637,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>39,42%</t>
+          <t>38,9%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,44%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4657,12 +4657,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>4032</t>
+          <t>3973</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>9314</t>
+          <t>9101</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4672,12 +4672,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>35,68%</t>
+          <t>35,17%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>82,43%</t>
+          <t>80,54%</t>
         </is>
       </c>
     </row>
@@ -5048,7 +5048,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>2494</t>
+          <t>2729</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5063,7 +5063,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>64,47%</t>
+          <t>70,55%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>3210</t>
+          <t>2634</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5133,7 +5133,7 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>48,32%</t>
+          <t>39,65%</t>
         </is>
       </c>
     </row>
@@ -5457,7 +5457,7 @@
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>3369</t>
+          <t>3842</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5472,7 +5472,7 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>50,71%</t>
+          <t>57,84%</t>
         </is>
       </c>
     </row>
@@ -5500,7 +5500,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>3144</t>
+          <t>3166</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5515,7 +5515,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>81,27%</t>
+          <t>81,85%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5570,7 +5570,7 @@
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>3742</t>
+          <t>3818</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5585,7 +5585,7 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>56,33%</t>
+          <t>57,47%</t>
         </is>
       </c>
     </row>
@@ -5608,12 +5608,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>647</t>
+          <t>646</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>3285</t>
+          <t>3275</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5623,12 +5623,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>84,92%</t>
+          <t>84,68%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5678,12 +5678,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>1428</t>
+          <t>1427</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>5462</t>
+          <t>5464</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5693,12 +5693,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>82,22%</t>
+          <t>82,25%</t>
         </is>
       </c>
     </row>
@@ -6408,7 +6408,7 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>2638</t>
+          <t>3220</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6423,7 +6423,7 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>48,33%</t>
+          <t>59,0%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6478,7 +6478,7 @@
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>3022</t>
+          <t>3049</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6493,7 +6493,7 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>28,9%</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>2820</t>
+          <t>2238</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -6531,7 +6531,7 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>51,67%</t>
+          <t>41,0%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
@@ -6586,7 +6586,7 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>7528</t>
+          <t>7501</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
@@ -6601,7 +6601,7 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>71,36%</t>
+          <t>71,1%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
@@ -6899,7 +6899,7 @@
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>3833</t>
+          <t>3850</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -6914,7 +6914,7 @@
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -6934,7 +6934,7 @@
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>3840</t>
+          <t>2958</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
@@ -6949,7 +6949,7 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>7,01%</t>
         </is>
       </c>
     </row>
@@ -7090,7 +7090,7 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>3885</t>
+          <t>4019</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -7105,7 +7105,7 @@
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -7160,7 +7160,7 @@
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>4454</t>
+          <t>4398</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
@@ -7175,7 +7175,7 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,43%</t>
         </is>
       </c>
     </row>
@@ -7424,12 +7424,12 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>1099</t>
+          <t>995</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>6624</t>
+          <t>6403</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -7439,12 +7439,12 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>32,08%</t>
+          <t>31,01%</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
@@ -7464,7 +7464,7 @@
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>8445</t>
+          <t>8314</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -7479,7 +7479,7 @@
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>39,23%</t>
+          <t>38,62%</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -7494,12 +7494,12 @@
       </c>
       <c r="S63" s="2" t="inlineStr">
         <is>
-          <t>4247</t>
+          <t>4302</t>
         </is>
       </c>
       <c r="T63" s="2" t="inlineStr">
         <is>
-          <t>12200</t>
+          <t>11866</t>
         </is>
       </c>
       <c r="U63" s="2" t="inlineStr">
@@ -7509,12 +7509,12 @@
       </c>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>28,14%</t>
         </is>
       </c>
     </row>
@@ -7537,12 +7537,12 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>3680</t>
+          <t>3840</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>10400</t>
+          <t>10877</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -7552,12 +7552,12 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>50,38%</t>
+          <t>52,68%</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -7572,12 +7572,12 @@
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>3242</t>
+          <t>3682</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>10450</t>
+          <t>10289</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -7587,12 +7587,12 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>48,54%</t>
+          <t>47,8%</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -7607,12 +7607,12 @@
       </c>
       <c r="S64" s="2" t="inlineStr">
         <is>
-          <t>8972</t>
+          <t>8812</t>
         </is>
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>18357</t>
+          <t>17994</t>
         </is>
       </c>
       <c r="U64" s="2" t="inlineStr">
@@ -7622,12 +7622,12 @@
       </c>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>43,53%</t>
+          <t>42,67%</t>
         </is>
       </c>
     </row>
@@ -7650,12 +7650,12 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>5675</t>
+          <t>5764</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>13218</t>
+          <t>13203</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -7665,12 +7665,12 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>27,92%</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>64,02%</t>
+          <t>63,95%</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -7685,12 +7685,12 @@
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>6211</t>
+          <t>6593</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>13547</t>
+          <t>13581</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -7700,12 +7700,12 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>62,93%</t>
+          <t>63,09%</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -7720,12 +7720,12 @@
       </c>
       <c r="S65" s="2" t="inlineStr">
         <is>
-          <t>14448</t>
+          <t>14473</t>
         </is>
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>25046</t>
+          <t>24634</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>34,26%</t>
+          <t>34,32%</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>59,39%</t>
+          <t>58,41%</t>
         </is>
       </c>
     </row>
@@ -9288,7 +9288,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3256</t>
+          <t>3230</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9303,7 +9303,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>70,85%</t>
+          <t>70,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9318,12 +9318,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>677</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4993</t>
+          <t>5120</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9333,12 +9333,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>66,25%</t>
+          <t>67,94%</t>
         </is>
       </c>
     </row>
@@ -9705,7 +9705,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2180</t>
+          <t>2940</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9720,7 +9720,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>74,15%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9740,7 +9740,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2965</t>
+          <t>2390</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9755,7 +9755,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>64,51%</t>
+          <t>52,01%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9775,7 +9775,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>4149</t>
+          <t>4275</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9790,7 +9790,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>55,06%</t>
+          <t>56,72%</t>
         </is>
       </c>
     </row>
@@ -9853,7 +9853,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2626</t>
+          <t>2594</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9868,7 +9868,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>57,13%</t>
+          <t>56,44%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9888,7 +9888,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2564</t>
+          <t>2689</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9903,7 +9903,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>35,68%</t>
         </is>
       </c>
     </row>
@@ -9961,12 +9961,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>558</t>
+          <t>563</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3391</t>
+          <t>3962</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9976,12 +9976,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>73,77%</t>
+          <t>86,21%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9996,12 +9996,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>637</t>
+          <t>667</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>4883</t>
+          <t>4798</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10011,12 +10011,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>64,8%</t>
+          <t>63,67%</t>
         </is>
       </c>
     </row>
@@ -10161,7 +10161,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2483</t>
+          <t>3215</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10176,7 +10176,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>54,41%</t>
+          <t>70,44%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2700</t>
+          <t>2929</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10246,7 +10246,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>30,91%</t>
         </is>
       </c>
     </row>
@@ -10269,12 +10269,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>479</t>
+          <t>475</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3815</t>
+          <t>3830</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10284,12 +10284,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>83,58%</t>
+          <t>83,92%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10304,12 +10304,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>697</t>
+          <t>693</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>4234</t>
+          <t>4220</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10319,12 +10319,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>86,18%</t>
+          <t>85,89%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10339,12 +10339,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1723</t>
+          <t>1582</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6825</t>
+          <t>6744</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>72,01%</t>
+          <t>71,16%</t>
         </is>
       </c>
     </row>
@@ -10726,7 +10726,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2771</t>
+          <t>2753</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -10741,7 +10741,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>60,71%</t>
+          <t>60,32%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -10761,7 +10761,7 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>2874</t>
+          <t>2975</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -10776,7 +10776,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>58,51%</t>
+          <t>60,55%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -10796,7 +10796,7 @@
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>4209</t>
+          <t>4253</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -10811,7 +10811,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>44,88%</t>
         </is>
       </c>
     </row>
@@ -10839,7 +10839,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2839</t>
+          <t>2720</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10854,7 +10854,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>62,2%</t>
+          <t>59,59%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10909,7 +10909,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3545</t>
+          <t>2796</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10924,7 +10924,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>37,41%</t>
+          <t>29,5%</t>
         </is>
       </c>
     </row>
@@ -10952,7 +10952,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3208</t>
+          <t>2583</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10967,7 +10967,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>70,28%</t>
+          <t>56,61%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10982,12 +10982,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>564</t>
+          <t>573</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>4120</t>
+          <t>4160</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10997,12 +10997,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>83,85%</t>
+          <t>84,67%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -11017,12 +11017,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>645</t>
+          <t>665</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>5345</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -11032,12 +11032,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>55,49%</t>
+          <t>56,4%</t>
         </is>
       </c>
     </row>
@@ -11177,12 +11177,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>458</t>
+          <t>456</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>4500</t>
+          <t>4443</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11192,12 +11192,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>33,56%</t>
+          <t>33,13%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11217,7 +11217,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>3122</t>
+          <t>3345</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11232,7 +11232,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11247,12 +11247,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>609</t>
+          <t>637</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>5326</t>
+          <t>5388</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11262,12 +11262,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>19,58%</t>
         </is>
       </c>
     </row>
@@ -11290,12 +11290,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>4076</t>
+          <t>3868</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>9975</t>
+          <t>9765</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11305,12 +11305,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>30,39%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>74,39%</t>
+          <t>72,82%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11325,12 +11325,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>4992</t>
+          <t>4533</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>10971</t>
+          <t>10840</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11340,12 +11340,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>35,4%</t>
+          <t>32,15%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>77,8%</t>
+          <t>76,87%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11360,12 +11360,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>10821</t>
+          <t>10693</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>19374</t>
+          <t>19279</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11375,12 +11375,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>39,33%</t>
+          <t>38,87%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>70,42%</t>
+          <t>70,08%</t>
         </is>
       </c>
     </row>
@@ -11742,12 +11742,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>518</t>
+          <t>540</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>5325</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -11757,12 +11757,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>39,42%</t>
+          <t>39,71%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -11777,12 +11777,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>1973</t>
+          <t>2153</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>7972</t>
+          <t>8252</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -11792,47 +11792,47 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
+          <t>15,27%</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>58,52%</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>6904</t>
+        </is>
+      </c>
+      <c r="S36" s="2" t="inlineStr">
+        <is>
+          <t>3850</t>
+        </is>
+      </c>
+      <c r="T36" s="2" t="inlineStr">
+        <is>
+          <t>11257</t>
+        </is>
+      </c>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>25,09%</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
           <t>13,99%</t>
         </is>
       </c>
-      <c r="P36" s="2" t="inlineStr">
-        <is>
-          <t>56,53%</t>
-        </is>
-      </c>
-      <c r="Q36" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="R36" s="2" t="inlineStr">
-        <is>
-          <t>6904</t>
-        </is>
-      </c>
-      <c r="S36" s="2" t="inlineStr">
-        <is>
-          <t>3432</t>
-        </is>
-      </c>
-      <c r="T36" s="2" t="inlineStr">
-        <is>
-          <t>10726</t>
-        </is>
-      </c>
-      <c r="U36" s="2" t="inlineStr">
-        <is>
-          <t>25,09%</t>
-        </is>
-      </c>
-      <c r="V36" s="2" t="inlineStr">
-        <is>
-          <t>12,48%</t>
-        </is>
-      </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>38,99%</t>
+          <t>40,92%</t>
         </is>
       </c>
     </row>
@@ -11860,7 +11860,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>4089</t>
+          <t>4209</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -11875,7 +11875,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>31,39%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -11930,7 +11930,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>4008</t>
+          <t>4421</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -11945,7 +11945,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>16,07%</t>
         </is>
       </c>
     </row>
@@ -11973,7 +11973,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>4652</t>
+          <t>4301</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -11988,7 +11988,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>34,69%</t>
+          <t>32,07%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -12008,7 +12008,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>3780</t>
+          <t>3234</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -12023,7 +12023,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -12038,12 +12038,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>447</t>
+          <t>446</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>5387</t>
+          <t>5330</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -12053,12 +12053,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>19,38%</t>
         </is>
       </c>
     </row>
@@ -12238,7 +12238,7 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>4962</t>
+          <t>4951</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -12253,7 +12253,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>50,66%</t>
+          <t>50,54%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -12273,7 +12273,7 @@
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>5413</t>
+          <t>5157</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -12288,7 +12288,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>26,05%</t>
         </is>
       </c>
     </row>
@@ -12311,12 +12311,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>1851</t>
+          <t>1907</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>6639</t>
+          <t>7173</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -12326,12 +12326,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>66,4%</t>
+          <t>71,74%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -12346,12 +12346,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>2071</t>
+          <t>2086</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>7193</t>
+          <t>7425</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -12361,12 +12361,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>21,3%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>73,43%</t>
+          <t>75,81%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -12381,12 +12381,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>5664</t>
+          <t>5556</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>12429</t>
+          <t>12887</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -12396,12 +12396,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>28,07%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>62,8%</t>
+          <t>65,11%</t>
         </is>
       </c>
     </row>
@@ -12763,12 +12763,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>1005</t>
+          <t>745</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>5856</t>
+          <t>5802</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -12778,12 +12778,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>58,56%</t>
+          <t>58,03%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -12803,7 +12803,7 @@
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>2727</t>
+          <t>2757</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -12818,7 +12818,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>28,15%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -12833,12 +12833,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>1333</t>
+          <t>1329</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>7540</t>
+          <t>7349</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -12848,12 +12848,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>38,09%</t>
+          <t>37,13%</t>
         </is>
       </c>
     </row>
@@ -12881,7 +12881,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>2744</t>
+          <t>3413</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -12896,7 +12896,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>34,13%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -12916,7 +12916,7 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>4360</t>
+          <t>4220</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -12931,7 +12931,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>44,52%</t>
+          <t>43,09%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -12946,12 +12946,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>635</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>5053</t>
+          <t>4960</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -12961,12 +12961,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,06%</t>
         </is>
       </c>
     </row>
@@ -12989,12 +12989,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>593</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>4485</t>
+          <t>4418</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -13004,12 +13004,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>44,85%</t>
+          <t>44,18%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -13029,7 +13029,7 @@
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>3996</t>
+          <t>4019</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -13044,7 +13044,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>40,8%</t>
+          <t>41,04%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -13059,12 +13059,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>1252</t>
+          <t>1243</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>6520</t>
+          <t>6479</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -13074,12 +13074,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>32,94%</t>
+          <t>32,73%</t>
         </is>
       </c>
     </row>
@@ -13372,7 +13372,7 @@
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>2661</t>
+          <t>2779</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -13387,7 +13387,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>53,68%</t>
+          <t>56,05%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -13407,7 +13407,7 @@
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>3320</t>
+          <t>3343</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -13422,7 +13422,7 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>43,43%</t>
+          <t>43,73%</t>
         </is>
       </c>
     </row>
@@ -13485,7 +13485,7 @@
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>2958</t>
+          <t>3144</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -13500,7 +13500,7 @@
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>59,66%</t>
+          <t>63,41%</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -13520,7 +13520,7 @@
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>3344</t>
+          <t>3078</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -13535,7 +13535,7 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>43,74%</t>
+          <t>40,26%</t>
         </is>
       </c>
     </row>
@@ -13932,7 +13932,7 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>1537</t>
+          <t>1572</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
@@ -13947,7 +13947,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>30,99%</t>
+          <t>31,7%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -13967,7 +13967,7 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>3798</t>
+          <t>3757</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
@@ -13982,7 +13982,7 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>49,67%</t>
+          <t>49,14%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
@@ -14240,12 +14240,12 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>640</t>
+          <t>634</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>5587</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -14255,12 +14255,12 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -14275,12 +14275,12 @@
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>638</t>
+          <t>646</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>7073</t>
+          <t>6310</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -14290,12 +14290,12 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -14310,12 +14310,12 @@
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>2080</t>
+          <t>2060</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>9527</t>
+          <t>8994</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
@@ -14325,12 +14325,12 @@
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,04%</t>
         </is>
       </c>
     </row>
@@ -14353,12 +14353,12 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>10641</t>
+          <t>11184</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>20240</t>
+          <t>20747</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -14368,12 +14368,12 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>30,43%</t>
+          <t>31,98%</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>57,87%</t>
+          <t>59,33%</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -14388,12 +14388,12 @@
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>12857</t>
+          <t>12824</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>22808</t>
+          <t>22970</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -14403,12 +14403,12 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>32,27%</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>57,4%</t>
+          <t>57,81%</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -14423,12 +14423,12 @@
       </c>
       <c r="S59" s="2" t="inlineStr">
         <is>
-          <t>26271</t>
+          <t>26558</t>
         </is>
       </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t>40083</t>
+          <t>39923</t>
         </is>
       </c>
       <c r="U59" s="2" t="inlineStr">
@@ -14438,12 +14438,12 @@
       </c>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>35,16%</t>
+          <t>35,55%</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>53,65%</t>
+          <t>53,44%</t>
         </is>
       </c>
     </row>
@@ -14506,7 +14506,7 @@
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>3414</t>
+          <t>3395</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -14521,7 +14521,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -14541,7 +14541,7 @@
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>2787</t>
+          <t>3419</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
@@ -14556,7 +14556,7 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>4,58%</t>
         </is>
       </c>
     </row>
@@ -14805,12 +14805,12 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>3881</t>
+          <t>3960</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>12248</t>
+          <t>12127</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -14820,12 +14820,12 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>35,02%</t>
+          <t>34,68%</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
@@ -14840,12 +14840,12 @@
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>3386</t>
+          <t>3566</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>11770</t>
+          <t>11734</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -14855,12 +14855,12 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>29,53%</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -14875,12 +14875,12 @@
       </c>
       <c r="S63" s="2" t="inlineStr">
         <is>
-          <t>9511</t>
+          <t>9087</t>
         </is>
       </c>
       <c r="T63" s="2" t="inlineStr">
         <is>
-          <t>22094</t>
+          <t>20699</t>
         </is>
       </c>
       <c r="U63" s="2" t="inlineStr">
@@ -14890,12 +14890,12 @@
       </c>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>27,71%</t>
         </is>
       </c>
     </row>
@@ -14918,12 +14918,12 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>2642</t>
+          <t>2629</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>9262</t>
+          <t>9758</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -14933,12 +14933,12 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>27,9%</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -14953,12 +14953,12 @@
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>3203</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>10881</t>
+          <t>10650</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -14968,12 +14968,12 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -14988,12 +14988,12 @@
       </c>
       <c r="S64" s="2" t="inlineStr">
         <is>
-          <t>7320</t>
+          <t>7382</t>
         </is>
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>17387</t>
+          <t>17194</t>
         </is>
       </c>
       <c r="U64" s="2" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>23,01%</t>
         </is>
       </c>
     </row>
@@ -15031,12 +15031,12 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>1996</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>8721</t>
+          <t>8914</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -15046,12 +15046,12 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -15066,12 +15066,12 @@
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>2601</t>
+          <t>2658</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>10307</t>
+          <t>9865</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -15081,12 +15081,12 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>24,83%</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -15101,12 +15101,12 @@
       </c>
       <c r="S65" s="2" t="inlineStr">
         <is>
-          <t>6033</t>
+          <t>6502</t>
         </is>
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>15726</t>
+          <t>15712</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
@@ -15116,12 +15116,12 @@
       </c>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>21,03%</t>
         </is>
       </c>
     </row>
@@ -15683,7 +15683,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2760</t>
+          <t>2740</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -15698,7 +15698,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>50,13%</t>
+          <t>49,76%</t>
         </is>
       </c>
     </row>
@@ -16135,7 +16135,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>3068</t>
+          <t>2876</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -16150,7 +16150,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>55,73%</t>
+          <t>52,25%</t>
         </is>
       </c>
     </row>
@@ -16356,7 +16356,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1917</t>
+          <t>2578</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -16371,7 +16371,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>34,82%</t>
+          <t>46,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -16556,7 +16556,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3294</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -16571,7 +16571,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>56,0%</t>
+          <t>58,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -16591,7 +16591,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3350</t>
+          <t>4114</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -16606,7 +16606,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>39,75%</t>
         </is>
       </c>
     </row>
@@ -16634,7 +16634,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2104</t>
+          <t>2247</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -16649,7 +16649,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>47,07%</t>
+          <t>50,29%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -16669,7 +16669,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3563</t>
+          <t>3810</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -16684,7 +16684,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>60,58%</t>
+          <t>64,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -16699,12 +16699,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>453</t>
+          <t>442</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4375</t>
+          <t>4295</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -16714,12 +16714,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>42,27%</t>
+          <t>41,49%</t>
         </is>
       </c>
     </row>
@@ -17081,7 +17081,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2365</t>
+          <t>2222</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -17096,7 +17096,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>52,93%</t>
+          <t>49,71%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -17151,12 +17151,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1613</t>
+          <t>1754</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>6659</t>
+          <t>6660</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -17166,12 +17166,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>64,33%</t>
+          <t>64,34%</t>
         </is>
       </c>
     </row>
@@ -17342,12 +17342,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1622</t>
+          <t>1648</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5882</t>
+          <t>5288</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -17357,12 +17357,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>89,9%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -17377,12 +17377,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1479</t>
+          <t>1351</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6946</t>
+          <t>6282</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -17392,12 +17392,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>67,11%</t>
+          <t>60,69%</t>
         </is>
       </c>
     </row>
@@ -17655,7 +17655,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3222</t>
+          <t>3225</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -17670,44 +17670,44 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
+          <t>84,99%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>1558</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>3556</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>37,21%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
           <t>84,92%</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>1558</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>3380</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>37,21%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>80,71%</t>
-        </is>
-      </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
           <t>5</t>
@@ -17720,12 +17720,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1384</t>
+          <t>1410</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6140</t>
+          <t>6107</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -17735,12 +17735,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>76,93%</t>
+          <t>76,51%</t>
         </is>
       </c>
     </row>
@@ -18107,7 +18107,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2564</t>
+          <t>2355</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -18122,7 +18122,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>67,58%</t>
+          <t>62,07%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -18142,7 +18142,7 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>2372</t>
+          <t>2580</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -18157,7 +18157,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>56,64%</t>
+          <t>61,6%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -18177,7 +18177,7 @@
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>3284</t>
+          <t>3834</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -18192,7 +18192,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>41,14%</t>
+          <t>48,03%</t>
         </is>
       </c>
     </row>
@@ -18333,7 +18333,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2529</t>
+          <t>3102</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -18348,7 +18348,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>66,67%</t>
+          <t>81,76%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -18363,12 +18363,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>575</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3528</t>
+          <t>3538</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -18378,12 +18378,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>84,25%</t>
+          <t>84,49%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -18398,12 +18398,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1226</t>
+          <t>1210</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5348</t>
+          <t>5523</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -18413,12 +18413,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>67,0%</t>
+          <t>69,2%</t>
         </is>
       </c>
     </row>
@@ -18563,7 +18563,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3061</t>
+          <t>3152</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -18578,7 +18578,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>28,06%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -18633,7 +18633,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2804</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -18648,7 +18648,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>10,49%</t>
         </is>
       </c>
     </row>
@@ -18671,12 +18671,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1365</t>
+          <t>1274</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>6289</t>
+          <t>6275</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -18686,12 +18686,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>55,98%</t>
+          <t>55,85%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -18706,12 +18706,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>4660</t>
+          <t>4603</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>11354</t>
+          <t>11157</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -18721,12 +18721,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>29,7%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>73,25%</t>
+          <t>71,98%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -18741,12 +18741,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>7376</t>
+          <t>7606</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>15489</t>
+          <t>15960</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -18756,12 +18756,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>28,45%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>57,94%</t>
+          <t>59,7%</t>
         </is>
       </c>
     </row>
@@ -18937,7 +18937,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>3372</t>
+          <t>3387</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -18952,7 +18952,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -18972,7 +18972,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>3873</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -18987,7 +18987,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>14,49%</t>
         </is>
       </c>
     </row>
@@ -19123,12 +19123,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>1347</t>
+          <t>1789</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>6719</t>
+          <t>6558</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -19138,12 +19138,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>59,8%</t>
+          <t>58,37%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -19158,12 +19158,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>617</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>5080</t>
+          <t>4611</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -19173,12 +19173,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>32,78%</t>
+          <t>29,75%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -19193,12 +19193,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>3016</t>
+          <t>3014</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>9528</t>
+          <t>10129</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -19208,12 +19208,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>35,64%</t>
+          <t>37,89%</t>
         </is>
       </c>
     </row>
@@ -19241,7 +19241,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2536</t>
+          <t>3212</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -19256,7 +19256,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>28,59%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -19276,7 +19276,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>3617</t>
+          <t>3636</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -19291,7 +19291,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -19311,7 +19311,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>4010</t>
+          <t>3884</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -19326,7 +19326,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>14,53%</t>
         </is>
       </c>
     </row>
@@ -19349,12 +19349,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>749</t>
+          <t>736</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>5788</t>
+          <t>6126</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -19364,12 +19364,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>51,52%</t>
+          <t>54,53%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -19384,12 +19384,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>1991</t>
+          <t>1985</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>7475</t>
+          <t>7696</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -19399,12 +19399,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>48,23%</t>
+          <t>49,66%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -19419,12 +19419,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>3792</t>
+          <t>3833</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>11310</t>
+          <t>11322</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -19434,12 +19434,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>42,31%</t>
+          <t>42,35%</t>
         </is>
       </c>
     </row>
@@ -19584,7 +19584,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>2326</t>
+          <t>2897</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -19599,7 +19599,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>38,63%</t>
+          <t>48,12%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -19619,7 +19619,7 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>3803</t>
+          <t>3791</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -19634,7 +19634,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>41,06%</t>
+          <t>40,93%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -19654,7 +19654,7 @@
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>4010</t>
+          <t>4166</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -19669,7 +19669,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>27,26%</t>
         </is>
       </c>
     </row>
@@ -19692,12 +19692,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>589</t>
+          <t>917</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>4166</t>
+          <t>4157</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -19707,12 +19707,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>69,2%</t>
+          <t>69,04%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -19732,7 +19732,7 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>6164</t>
+          <t>6122</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -19747,7 +19747,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>66,54%</t>
+          <t>66,09%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -19762,12 +19762,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>2565</t>
+          <t>2821</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>8286</t>
+          <t>8710</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -19777,12 +19777,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>54,22%</t>
+          <t>56,99%</t>
         </is>
       </c>
     </row>
@@ -19845,7 +19845,7 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>3078</t>
+          <t>3733</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -19860,7 +19860,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>33,23%</t>
+          <t>40,3%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -19880,7 +19880,7 @@
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>3728</t>
+          <t>3497</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -19895,7 +19895,7 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>22,88%</t>
         </is>
       </c>
     </row>
@@ -20071,7 +20071,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>3206</t>
+          <t>3923</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -20086,7 +20086,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>34,61%</t>
+          <t>42,35%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -20106,7 +20106,7 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>4023</t>
+          <t>5251</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -20121,7 +20121,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>34,36%</t>
         </is>
       </c>
     </row>
@@ -20149,7 +20149,7 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>2586</t>
+          <t>2635</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -20164,7 +20164,7 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>42,95%</t>
+          <t>43,77%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -20184,7 +20184,7 @@
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>3673</t>
+          <t>3698</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -20199,7 +20199,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>39,65%</t>
+          <t>39,92%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -20219,7 +20219,7 @@
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>4225</t>
+          <t>4290</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -20234,7 +20234,7 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>28,07%</t>
         </is>
       </c>
     </row>
@@ -20262,7 +20262,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>2521</t>
+          <t>2548</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -20277,7 +20277,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>41,88%</t>
+          <t>42,32%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -20332,7 +20332,7 @@
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>3104</t>
+          <t>3116</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -20347,7 +20347,7 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>20,39%</t>
         </is>
       </c>
     </row>
@@ -20370,12 +20370,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>592</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>4290</t>
+          <t>3911</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -20385,12 +20385,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>71,24%</t>
+          <t>64,96%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -20405,12 +20405,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>749</t>
+          <t>716</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>5765</t>
+          <t>5645</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -20420,12 +20420,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>62,24%</t>
+          <t>60,94%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -20440,12 +20440,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>2248</t>
+          <t>2118</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>8340</t>
+          <t>8204</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -20455,12 +20455,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>54,57%</t>
+          <t>53,68%</t>
         </is>
       </c>
     </row>
@@ -20788,7 +20788,7 @@
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>2988</t>
+          <t>2837</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -20803,7 +20803,7 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>65,66%</t>
+          <t>62,34%</t>
         </is>
       </c>
     </row>
@@ -21348,7 +21348,7 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>1562</t>
+          <t>1713</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
@@ -21363,7 +21363,7 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>34,34%</t>
+          <t>37,66%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
@@ -21626,7 +21626,7 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>4100</t>
+          <t>3750</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -21641,7 +21641,7 @@
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -21661,7 +21661,7 @@
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>4474</t>
+          <t>5497</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -21676,7 +21676,7 @@
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -21691,12 +21691,12 @@
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>755</t>
+          <t>741</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>6497</t>
+          <t>6636</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
@@ -21706,12 +21706,12 @@
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,42%</t>
         </is>
       </c>
     </row>
@@ -21734,12 +21734,12 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>5393</t>
+          <t>5746</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>13144</t>
+          <t>13475</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -21749,12 +21749,12 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>48,09%</t>
+          <t>49,3%</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -21769,12 +21769,12 @@
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>9652</t>
+          <t>9730</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>19339</t>
+          <t>19799</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -21784,12 +21784,12 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>44,9%</t>
+          <t>45,96%</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -21804,12 +21804,12 @@
       </c>
       <c r="S59" s="2" t="inlineStr">
         <is>
-          <t>17339</t>
+          <t>17095</t>
         </is>
       </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t>29596</t>
+          <t>29510</t>
         </is>
       </c>
       <c r="U59" s="2" t="inlineStr">
@@ -21819,12 +21819,12 @@
       </c>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>42,04%</t>
+          <t>41,91%</t>
         </is>
       </c>
     </row>
@@ -21887,7 +21887,7 @@
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>3863</t>
+          <t>3695</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -21902,7 +21902,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -21922,7 +21922,7 @@
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>4269</t>
+          <t>4045</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
@@ -21937,7 +21937,7 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>5,75%</t>
         </is>
       </c>
     </row>
@@ -22000,7 +22000,7 @@
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>3433</t>
+          <t>3824</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -22015,7 +22015,7 @@
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -22035,7 +22035,7 @@
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>3339</t>
+          <t>3770</t>
         </is>
       </c>
       <c r="U61" s="2" t="inlineStr">
@@ -22050,7 +22050,7 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>5,35%</t>
         </is>
       </c>
     </row>
@@ -22113,7 +22113,7 @@
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>4102</t>
+          <t>4734</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -22128,7 +22128,7 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -22148,7 +22148,7 @@
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>4065</t>
+          <t>4514</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
@@ -22163,7 +22163,7 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>6,41%</t>
         </is>
       </c>
     </row>
@@ -22186,12 +22186,12 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>6012</t>
+          <t>5887</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>13793</t>
+          <t>14069</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -22201,12 +22201,12 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>50,47%</t>
+          <t>51,48%</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
@@ -22221,12 +22221,12 @@
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>1248</t>
+          <t>1317</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>7283</t>
+          <t>7099</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -22256,12 +22256,12 @@
       </c>
       <c r="S63" s="2" t="inlineStr">
         <is>
-          <t>8725</t>
+          <t>8525</t>
         </is>
       </c>
       <c r="T63" s="2" t="inlineStr">
         <is>
-          <t>19081</t>
+          <t>18998</t>
         </is>
       </c>
       <c r="U63" s="2" t="inlineStr">
@@ -22271,12 +22271,12 @@
       </c>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>26,98%</t>
         </is>
       </c>
     </row>
@@ -22304,7 +22304,7 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>3891</t>
+          <t>3598</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -22319,7 +22319,7 @@
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -22334,12 +22334,12 @@
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>2165</t>
+          <t>1511</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>9611</t>
+          <t>9029</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -22349,12 +22349,12 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -22369,12 +22369,12 @@
       </c>
       <c r="S64" s="2" t="inlineStr">
         <is>
-          <t>2593</t>
+          <t>2811</t>
         </is>
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>11014</t>
+          <t>10960</t>
         </is>
       </c>
       <c r="U64" s="2" t="inlineStr">
@@ -22384,12 +22384,12 @@
       </c>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,57%</t>
         </is>
       </c>
     </row>
@@ -22412,12 +22412,12 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>3255</t>
+          <t>3025</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>10867</t>
+          <t>10010</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -22427,12 +22427,12 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>39,76%</t>
+          <t>36,63%</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -22447,12 +22447,12 @@
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>11810</t>
+          <t>12064</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>23217</t>
+          <t>22311</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -22462,12 +22462,12 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>28,01%</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>53,9%</t>
+          <t>51,8%</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -22482,12 +22482,12 @@
       </c>
       <c r="S65" s="2" t="inlineStr">
         <is>
-          <t>17548</t>
+          <t>17486</t>
         </is>
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>31112</t>
+          <t>30450</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
@@ -22497,12 +22497,12 @@
       </c>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>24,84%</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>44,19%</t>
+          <t>43,25%</t>
         </is>
       </c>
     </row>
@@ -23177,7 +23177,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>3883</t>
+          <t>3621</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -23192,7 +23192,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>64,64%</t>
+          <t>60,28%</t>
         </is>
       </c>
     </row>
@@ -23511,12 +23511,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>711</t>
+          <t>991</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>5182</t>
+          <t>5149</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -23526,12 +23526,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>86,25%</t>
+          <t>85,7%</t>
         </is>
       </c>
     </row>
@@ -23742,7 +23742,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>4579</t>
+          <t>4606</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -23757,7 +23757,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>76,21%</t>
+          <t>76,66%</t>
         </is>
       </c>
     </row>
@@ -24080,12 +24080,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>656</t>
+          <t>653</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4948</t>
+          <t>4667</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -24095,12 +24095,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>77,91%</t>
+          <t>73,48%</t>
         </is>
       </c>
     </row>
@@ -24198,7 +24198,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>4275</t>
+          <t>4443</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -24213,7 +24213,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>67,31%</t>
+          <t>69,96%</t>
         </is>
       </c>
     </row>
@@ -24389,7 +24389,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3071</t>
+          <t>2957</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -24404,7 +24404,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>84,24%</t>
+          <t>81,12%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -24424,7 +24424,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3772</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -24439,7 +24439,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>59,39%</t>
+          <t>58,44%</t>
         </is>
       </c>
     </row>
@@ -24532,12 +24532,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>319</t>
+          <t>323</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>3203</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -24547,12 +24547,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>50,44%</t>
+          <t>51,85%</t>
         </is>
       </c>
     </row>
@@ -25071,7 +25071,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3140</t>
+          <t>3141</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -25086,7 +25086,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>56,05%</t>
+          <t>56,09%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -25106,7 +25106,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3062</t>
+          <t>3872</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -25121,7 +25121,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>38,99%</t>
         </is>
       </c>
     </row>
@@ -25149,7 +25149,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3513</t>
+          <t>2774</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -25164,7 +25164,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>81,13%</t>
+          <t>64,07%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -25184,7 +25184,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3534</t>
+          <t>3592</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -25199,7 +25199,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>63,1%</t>
+          <t>64,13%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -25219,7 +25219,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>4752</t>
+          <t>4701</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -25234,7 +25234,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>47,85%</t>
+          <t>47,33%</t>
         </is>
       </c>
     </row>
@@ -25483,12 +25483,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>763</t>
+          <t>745</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3780</t>
+          <t>3776</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -25498,12 +25498,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>87,31%</t>
+          <t>87,2%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -25518,12 +25518,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>843</t>
+          <t>1018</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>4856</t>
+          <t>4888</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -25533,12 +25533,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>86,7%</t>
+          <t>87,27%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -25553,12 +25553,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>2433</t>
+          <t>2574</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7831</t>
+          <t>7844</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -25568,12 +25568,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>25,91%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>78,86%</t>
+          <t>78,98%</t>
         </is>
       </c>
     </row>
@@ -25636,7 +25636,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3599</t>
+          <t>3408</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -25651,7 +25651,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>64,26%</t>
+          <t>60,84%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -25671,7 +25671,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4186</t>
+          <t>4540</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -25686,7 +25686,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>42,15%</t>
+          <t>45,71%</t>
         </is>
       </c>
     </row>
@@ -25714,7 +25714,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3485</t>
+          <t>3002</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -25729,7 +25729,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>80,48%</t>
+          <t>69,33%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -25784,7 +25784,7 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4483</t>
+          <t>3796</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -25799,7 +25799,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>45,14%</t>
+          <t>38,23%</t>
         </is>
       </c>
     </row>
@@ -26057,7 +26057,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>3481</t>
+          <t>3359</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -26072,7 +26072,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>42,31%</t>
+          <t>40,82%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -26092,7 +26092,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2706</t>
+          <t>3280</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -26107,7 +26107,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>37,2%</t>
+          <t>45,09%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -26127,7 +26127,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>4069</t>
+          <t>4788</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -26142,7 +26142,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>30,88%</t>
         </is>
       </c>
     </row>
@@ -26165,12 +26165,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>765</t>
+          <t>754</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>4744</t>
+          <t>5068</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -26180,12 +26180,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>57,65%</t>
+          <t>61,59%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -26200,12 +26200,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>423</t>
+          <t>409</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>5075</t>
+          <t>4818</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -26215,12 +26215,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>69,75%</t>
+          <t>66,23%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -26235,12 +26235,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1764</t>
+          <t>1697</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>7625</t>
+          <t>8195</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -26250,12 +26250,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>49,18%</t>
+          <t>52,86%</t>
         </is>
       </c>
     </row>
@@ -26431,7 +26431,7 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>3981</t>
+          <t>3699</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -26446,7 +26446,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>54,72%</t>
+          <t>50,85%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -26466,7 +26466,7 @@
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>4887</t>
+          <t>4910</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -26481,7 +26481,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>31,67%</t>
         </is>
       </c>
     </row>
@@ -26504,12 +26504,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>1229</t>
+          <t>1097</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>5754</t>
+          <t>5667</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -26519,12 +26519,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>69,93%</t>
+          <t>68,88%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -26574,12 +26574,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1145</t>
+          <t>1186</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>6504</t>
+          <t>6863</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -26589,12 +26589,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>41,96%</t>
+          <t>44,27%</t>
         </is>
       </c>
     </row>
@@ -26622,7 +26622,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2867</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -26637,7 +26637,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>39,27%</t>
+          <t>34,84%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -26652,12 +26652,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>439</t>
+          <t>429</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>4146</t>
+          <t>4018</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -26667,12 +26667,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>56,99%</t>
+          <t>55,23%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -26687,12 +26687,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>584</t>
+          <t>600</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>5186</t>
+          <t>5021</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -26702,12 +26702,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>33,45%</t>
+          <t>32,39%</t>
         </is>
       </c>
     </row>
@@ -26735,7 +26735,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>3792</t>
+          <t>4045</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -26750,7 +26750,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>46,09%</t>
+          <t>49,16%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -26770,7 +26770,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>4381</t>
+          <t>4772</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -26785,7 +26785,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>60,22%</t>
+          <t>65,6%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -26800,12 +26800,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>884</t>
+          <t>861</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>6629</t>
+          <t>6585</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -26815,12 +26815,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>42,76%</t>
+          <t>42,47%</t>
         </is>
       </c>
     </row>
@@ -27078,7 +27078,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>3809</t>
+          <t>4358</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -27093,7 +27093,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>26,21%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -27148,7 +27148,7 @@
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>4158</t>
+          <t>4074</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -27163,7 +27163,7 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,27%</t>
         </is>
       </c>
     </row>
@@ -27186,12 +27186,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>4453</t>
+          <t>4623</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>13359</t>
+          <t>13034</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -27201,12 +27201,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>80,35%</t>
+          <t>78,39%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -27221,12 +27221,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>3365</t>
+          <t>3028</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>10446</t>
+          <t>10106</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -27236,12 +27236,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>63,0%</t>
+          <t>60,95%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -27256,12 +27256,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>9609</t>
+          <t>9704</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>20878</t>
+          <t>21360</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -27271,12 +27271,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>29,22%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>62,87%</t>
+          <t>64,32%</t>
         </is>
       </c>
     </row>
@@ -27417,7 +27417,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>4187</t>
+          <t>4380</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -27432,7 +27432,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>26,34%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -27452,7 +27452,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>3656</t>
+          <t>3373</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -27467,7 +27467,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -27482,12 +27482,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>479</t>
+          <t>356</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>5149</t>
+          <t>5605</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -27497,12 +27497,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>16,88%</t>
         </is>
       </c>
     </row>
@@ -27525,12 +27525,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>650</t>
+          <t>722</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>6361</t>
+          <t>6266</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -27540,12 +27540,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>38,26%</t>
+          <t>37,69%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -27560,12 +27560,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>1752</t>
+          <t>1489</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>7822</t>
+          <t>7500</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -27575,12 +27575,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>47,18%</t>
+          <t>45,23%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -27595,12 +27595,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>3115</t>
+          <t>3183</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>11679</t>
+          <t>11179</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -27610,12 +27610,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>35,17%</t>
+          <t>33,66%</t>
         </is>
       </c>
     </row>
@@ -27638,12 +27638,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>832</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>6176</t>
+          <t>6387</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -27653,12 +27653,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>37,15%</t>
+          <t>38,41%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -27673,12 +27673,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>1159</t>
+          <t>1292</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>7060</t>
+          <t>7211</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -27688,12 +27688,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>42,58%</t>
+          <t>43,49%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -27708,12 +27708,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>3210</t>
+          <t>3027</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>11368</t>
+          <t>11314</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -27723,12 +27723,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>34,07%</t>
         </is>
       </c>
     </row>
@@ -27756,7 +27756,7 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>4208</t>
+          <t>4214</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -27771,7 +27771,7 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -27791,7 +27791,7 @@
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>4435</t>
+          <t>3977</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -27806,7 +27806,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -27821,12 +27821,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>665</t>
+          <t>671</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>5651</t>
+          <t>6241</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -27836,12 +27836,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>18,8%</t>
         </is>
       </c>
     </row>
@@ -28099,7 +28099,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>4147</t>
+          <t>3747</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -28114,7 +28114,7 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>50,39%</t>
+          <t>45,53%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -28134,7 +28134,7 @@
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>2231</t>
+          <t>2064</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -28149,7 +28149,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>29,27%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -28164,12 +28164,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>368</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>4726</t>
+          <t>4405</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -28179,12 +28179,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>28,82%</t>
         </is>
       </c>
     </row>
@@ -28212,7 +28212,7 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>3716</t>
+          <t>3836</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -28227,7 +28227,7 @@
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>45,14%</t>
+          <t>46,61%</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -28247,7 +28247,7 @@
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>3741</t>
+          <t>3881</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -28262,7 +28262,7 @@
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>53,05%</t>
+          <t>55,03%</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -28277,12 +28277,12 @@
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>538</t>
+          <t>544</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>5462</t>
+          <t>5663</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -28292,12 +28292,12 @@
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>35,74%</t>
+          <t>37,06%</t>
         </is>
       </c>
     </row>
@@ -28438,7 +28438,7 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>3541</t>
+          <t>3759</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -28453,7 +28453,7 @@
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>43,02%</t>
+          <t>45,66%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -28508,7 +28508,7 @@
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>3688</t>
+          <t>4039</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -28523,7 +28523,7 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>26,43%</t>
         </is>
       </c>
     </row>
@@ -28551,7 +28551,7 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>4506</t>
+          <t>4390</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -28566,7 +28566,7 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>54,74%</t>
+          <t>53,33%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -28621,7 +28621,7 @@
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>4300</t>
+          <t>4986</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -28636,7 +28636,7 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>32,62%</t>
         </is>
       </c>
     </row>
@@ -28659,12 +28659,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>671</t>
+          <t>653</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>6292</t>
+          <t>6009</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -28674,12 +28674,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>76,45%</t>
+          <t>73,0%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -28694,12 +28694,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>1822</t>
+          <t>1629</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>6481</t>
+          <t>6153</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -28709,12 +28709,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>91,9%</t>
+          <t>87,24%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -28729,12 +28729,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>3571</t>
+          <t>3797</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>10878</t>
+          <t>11027</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -28744,12 +28744,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>24,84%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>71,18%</t>
+          <t>72,15%</t>
         </is>
       </c>
     </row>
@@ -28777,7 +28777,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>5145</t>
+          <t>4750</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -28792,7 +28792,7 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>62,5%</t>
+          <t>57,71%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -28812,7 +28812,7 @@
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>3831</t>
+          <t>4175</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -28827,7 +28827,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>54,33%</t>
+          <t>59,2%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -28847,7 +28847,7 @@
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>6472</t>
+          <t>6210</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -28862,7 +28862,7 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>42,35%</t>
+          <t>40,63%</t>
         </is>
       </c>
     </row>
@@ -29115,12 +29115,12 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>1994</t>
+          <t>2085</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>9447</t>
+          <t>9793</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -29130,12 +29130,12 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -29150,12 +29150,12 @@
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>386</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>4854</t>
+          <t>4669</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -29165,12 +29165,12 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -29185,12 +29185,12 @@
       </c>
       <c r="S59" s="2" t="inlineStr">
         <is>
-          <t>3220</t>
+          <t>3530</t>
         </is>
       </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t>11590</t>
+          <t>12355</t>
         </is>
       </c>
       <c r="U59" s="2" t="inlineStr">
@@ -29200,12 +29200,12 @@
       </c>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>14,32%</t>
         </is>
       </c>
     </row>
@@ -29228,12 +29228,12 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>7594</t>
+          <t>7799</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>21327</t>
+          <t>20750</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -29243,12 +29243,12 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>51,52%</t>
+          <t>50,12%</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -29263,12 +29263,12 @@
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>7739</t>
+          <t>8136</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>19282</t>
+          <t>18896</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -29278,12 +29278,12 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>42,96%</t>
+          <t>42,1%</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -29298,12 +29298,12 @@
       </c>
       <c r="S60" s="2" t="inlineStr">
         <is>
-          <t>18496</t>
+          <t>18576</t>
         </is>
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>35795</t>
+          <t>35441</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
@@ -29313,12 +29313,12 @@
       </c>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>41,49%</t>
+          <t>41,07%</t>
         </is>
       </c>
     </row>
@@ -29459,7 +29459,7 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>5694</t>
+          <t>5059</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -29474,7 +29474,7 @@
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -29489,12 +29489,12 @@
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>856</t>
+          <t>746</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>6988</t>
+          <t>7081</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -29504,12 +29504,12 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -29524,12 +29524,12 @@
       </c>
       <c r="S62" s="2" t="inlineStr">
         <is>
-          <t>1877</t>
+          <t>1811</t>
         </is>
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>9694</t>
+          <t>10048</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
@@ -29539,12 +29539,12 @@
       </c>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,65%</t>
         </is>
       </c>
     </row>
@@ -29567,12 +29567,12 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>6135</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>15764</t>
+          <t>16401</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -29582,12 +29582,12 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>38,08%</t>
+          <t>39,62%</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
@@ -29602,12 +29602,12 @@
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>6664</t>
+          <t>6562</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>16621</t>
+          <t>16815</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -29617,12 +29617,12 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>37,03%</t>
+          <t>37,46%</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -29637,12 +29637,12 @@
       </c>
       <c r="S63" s="2" t="inlineStr">
         <is>
-          <t>15178</t>
+          <t>14642</t>
         </is>
       </c>
       <c r="T63" s="2" t="inlineStr">
         <is>
-          <t>28658</t>
+          <t>28767</t>
         </is>
       </c>
       <c r="U63" s="2" t="inlineStr">
@@ -29652,12 +29652,12 @@
       </c>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>33,21%</t>
+          <t>33,34%</t>
         </is>
       </c>
     </row>
@@ -29680,12 +29680,12 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>3219</t>
+          <t>3229</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>11808</t>
+          <t>11797</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -29695,12 +29695,12 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>28,5%</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -29715,12 +29715,12 @@
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>5909</t>
+          <t>6516</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>16258</t>
+          <t>15974</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -29730,12 +29730,12 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>36,22%</t>
+          <t>35,59%</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -29750,12 +29750,12 @@
       </c>
       <c r="S64" s="2" t="inlineStr">
         <is>
-          <t>11327</t>
+          <t>10951</t>
         </is>
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>24342</t>
+          <t>24267</t>
         </is>
       </c>
       <c r="U64" s="2" t="inlineStr">
@@ -29765,12 +29765,12 @@
       </c>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>28,12%</t>
         </is>
       </c>
     </row>
@@ -29793,12 +29793,12 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>2163</t>
+          <t>2088</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>10556</t>
+          <t>9883</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -29808,12 +29808,12 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -29828,12 +29828,12 @@
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>2655</t>
+          <t>2355</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>11453</t>
+          <t>11449</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -29843,7 +29843,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -29863,12 +29863,12 @@
       </c>
       <c r="S65" s="2" t="inlineStr">
         <is>
-          <t>6373</t>
+          <t>6457</t>
         </is>
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>17438</t>
+          <t>18021</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
@@ -29878,12 +29878,12 @@
       </c>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>20,89%</t>
         </is>
       </c>
     </row>
